--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +804,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -998,7 +1006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1045,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1056,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1084,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1109,7 +1121,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1145,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1165,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1286,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1347,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1397,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1458,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1508,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1516,22 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1548,12 +1564,12 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1567,7 +1583,7 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1603,7 +1619,784 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,14 +819,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -862,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,17 +923,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -939,13 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -973,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1006,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1030,17 +1042,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1050,13 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1094,24 +1110,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1121,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1160,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1236,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1260,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1386,7 +1410,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1397,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1497,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1508,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1619,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1719,7 +1743,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1730,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1841,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1952,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2063,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2174,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2279,13 +2303,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2293,22 +2321,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2346,7 +2374,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2360,43 +2388,836 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>—/13</t>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1449,32 +1449,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,17 +1510,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1526,13 +1530,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1632,7 +1640,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1704,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1815,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1926,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2382,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2612,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2830,7 +2838,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2884,7 +2892,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2953,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,7 +3064,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3100,13 +3108,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3179,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3221,6 +3233,117 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,18 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1601,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1712,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,32 +1794,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1823,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1847,33 +1855,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1901,32 +1913,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1934,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1958,33 +1974,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2012,32 +2032,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2045,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2069,33 +2093,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2123,32 +2151,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2156,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2180,33 +2212,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2306,7 +2342,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2382,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2536,7 +2572,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2612,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2892,7 +2928,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3215,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,7 +3326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3344,6 +3380,696 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,18 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,18 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,18 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1875,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1994,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2123,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2173,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -2188,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2237,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2270,32 +2282,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2303,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2327,17 +2343,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2347,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2385,32 +2401,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2418,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2442,37 +2462,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2500,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2533,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2557,17 +2581,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2577,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2702,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2730,32 +2754,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -2763,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2787,33 +2815,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2841,32 +2873,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2874,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2898,37 +2934,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2956,32 +2992,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2989,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3013,33 +3053,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3067,32 +3111,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -3100,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3124,17 +3172,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3144,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3182,32 +3230,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3215,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3239,33 +3291,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3293,32 +3349,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -3326,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3350,33 +3410,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3404,32 +3468,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3437,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3461,17 +3529,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3481,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3519,32 +3587,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3552,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3576,17 +3648,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3596,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3706,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3721,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3831,12 +3903,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3941,17 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3959,22 +4031,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4012,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4026,47 +4098,967 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3240,24 +3240,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3597,24 +3597,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3706,32 +3706,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3763,17 +3767,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3783,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3821,32 +3825,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -3854,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3878,37 +3886,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4008,7 +4016,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4023,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4051,32 +4059,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4084,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4108,17 +4120,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4128,17 +4140,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4166,32 +4178,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4199,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4223,37 +4239,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4281,32 +4297,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4314,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4338,17 +4358,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4358,17 +4378,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4468,7 +4488,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4483,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4511,32 +4531,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4544,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4568,37 +4592,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4713,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4823,12 +4847,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4951,22 +4975,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4999,12 +5023,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5018,47 +5042,737 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,14 +823,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>88.5</t>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,14 +2477,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,14 +3544,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>88.5</t>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,14 +4135,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4416,32 +4416,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -4449,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4473,17 +4477,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4493,17 +4497,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4541,24 +4545,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4568,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4650,32 +4654,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4683,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4707,17 +4715,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4727,17 +4735,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4765,32 +4773,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4798,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4822,17 +4834,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4842,17 +4854,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4880,32 +4892,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -4913,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,27 +4953,27 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4967,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4995,32 +5011,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5028,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5052,17 +5072,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5072,17 +5092,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5110,32 +5130,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -5143,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5167,37 +5191,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5373,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5412,7 +5436,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5488,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5542,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5647,17 +5671,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5767,12 +5791,702 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,12 +4021,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,22 +4492,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5140,24 +5140,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5249,32 +5249,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5282,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,17 +5310,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5326,12 +5330,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5364,32 +5368,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -5397,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5421,17 +5429,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5441,12 +5449,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5479,32 +5487,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5512,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5536,17 +5548,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5556,17 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5594,32 +5606,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -5627,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5651,37 +5667,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5725,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -5742,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,17 +5786,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5786,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,32 +5959,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>64分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5972,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5996,37 +6020,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6136,7 +6160,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6202,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6256,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6361,12 +6385,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6432,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6486,7 +6510,467 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
           <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,17 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5616,24 +5616,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5844,32 +5844,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5901,17 +5905,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5921,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5969,24 +5973,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>64分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5996,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6078,32 +6082,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -6111,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,17 +6143,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6155,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6193,32 +6201,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6226,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,37 +6262,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6456,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6495,7 +6507,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6510,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6620,12 +6632,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6801,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6850,12 +6862,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6974,6 +6986,351 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,14 +1533,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,17 +4497,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5449,17 +5449,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,17 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6320,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -6353,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,17 +6381,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6397,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6435,32 +6439,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6468,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,17 +6500,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6512,17 +6520,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6550,32 +6558,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -6583,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,17 +6619,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6627,17 +6639,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6737,7 +6749,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6813,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6928,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7043,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7097,7 +7109,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7207,12 +7219,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7220,22 +7232,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7268,12 +7280,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7312,22 +7324,367 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>8/14</t>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,17 +4140,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,22 +4849,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6282,17 +6282,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6330,24 +6330,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6449,24 +6449,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6677,32 +6677,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6710,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,17 +6738,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6754,17 +6758,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6792,32 +6796,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6825,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6849,17 +6857,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6869,12 +6877,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6907,32 +6915,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6940,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,37 +6976,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7022,32 +7034,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7055,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7079,37 +7095,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7137,32 +7153,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7170,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7194,17 +7214,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7214,17 +7234,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7324,7 +7344,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7400,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7449,12 +7469,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,17 +7694,707 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>2/14</t>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,14 +2120,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,14 +2239,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>81.5</t>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,14 +3544,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,14 +3782,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,14 +3901,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>81.5</t>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,14 +5444,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>81.5</t>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,22 +5801,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,14 +6039,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,14 +6158,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,22 +6277,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>81.5</t>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,17 +6520,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6872,14 +6872,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7229,22 +7229,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7272,32 +7272,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -7305,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7329,17 +7333,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7349,17 +7353,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7387,32 +7391,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7420,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7444,17 +7452,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7464,17 +7472,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7502,32 +7510,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7535,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,32 +7571,32 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7617,32 +7629,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7650,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,17 +7690,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7694,12 +7710,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7732,32 +7748,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -7765,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7789,37 +7809,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7847,32 +7867,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7880,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7904,17 +7928,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7924,12 +7948,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7995,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8034,7 +8058,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8110,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8159,7 +8183,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8225,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,22 +8311,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A12050A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8335,12 +8359,12 @@
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8354,47 +8378,852 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
         <is>
           <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,12 +2001,12 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,14 +2830,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,22 +3425,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,22 +4968,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,14 +5682,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,22 +5920,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,14 +6634,14 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7758,24 +7758,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7877,24 +7877,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7986,32 +7986,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8019,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,17 +8047,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8063,12 +8067,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8101,32 +8105,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8134,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8158,27 +8166,27 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8216,32 +8224,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -8249,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,37 +8285,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8331,32 +8343,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -8364,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8388,37 +8404,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8446,32 +8462,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -8479,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8503,17 +8523,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8523,12 +8543,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8594,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8633,7 +8653,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8648,7 +8668,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8763,7 +8783,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8939,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8993,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9103,7 +9123,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9116,22 +9136,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9169,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9183,47 +9203,967 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>83.5</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,22 +2711,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,22 +3901,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,22 +5325,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,22 +5801,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,22 +6396,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,22 +6515,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,17 +6877,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7467,22 +7467,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7586,22 +7586,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,22 +7824,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,17 +8067,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8472,24 +8472,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8581,32 +8581,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8614,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8638,17 +8642,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8658,17 +8662,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8768,7 +8772,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8783,7 +8787,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8811,32 +8815,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8844,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,37 +8876,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8926,32 +8934,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -8959,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8983,37 +8995,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9041,32 +9053,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9074,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9098,37 +9114,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9156,32 +9172,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9189,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9213,37 +9233,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9343,7 +9363,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9386,32 +9406,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9419,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9443,17 +9467,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9463,17 +9487,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9649,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9688,7 +9712,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9703,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9813,12 +9837,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9994,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10038,17 +10062,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10167,6 +10191,811 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>80.4</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,17 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,17 +4730,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,22 +4849,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,22 +5325,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6753,17 +6753,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,17 +6877,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6991,22 +6991,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,22 +7110,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7586,22 +7586,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7705,17 +7705,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7943,22 +7943,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8181,22 +8181,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8305,17 +8305,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8419,22 +8419,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8662,17 +8662,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8891,22 +8891,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9063,19 +9063,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9291,32 +9291,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -9324,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9348,17 +9352,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9368,12 +9372,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9416,24 +9420,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9443,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9492,7 +9496,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9525,32 +9529,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9558,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9582,32 +9590,32 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9640,32 +9648,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -9673,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9697,17 +9709,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9717,17 +9729,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9755,32 +9767,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -9788,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9812,37 +9828,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9870,32 +9886,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9903,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9927,37 +9947,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9985,32 +10005,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10018,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10042,17 +10066,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10062,17 +10086,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10100,32 +10124,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10133,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10157,37 +10185,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10363,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10417,7 +10445,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10445,32 +10473,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10478,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10502,37 +10534,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10647,7 +10679,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10752,12 +10784,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10823,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10872,7 +10904,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10885,22 +10917,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10933,12 +10965,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10952,47 +10984,622 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8896,17 +8896,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10146,12 +10146,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10243,32 +10243,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10276,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10304,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10320,7 +10324,7 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
@@ -10391,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10473,36 +10477,32 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10534,17 +10534,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10554,17 +10554,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11589,17 +11589,132 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>81.7</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
-        <is>
-          <t>10/14</t>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,22 +3425,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,22 +4968,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5449,17 +5449,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,22 +5920,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8300,22 +8300,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9015,17 +9015,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9134,17 +9134,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9253,12 +9253,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,12 +9372,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9724,22 +9724,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10362,32 +10362,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -10395,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10419,17 +10423,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10439,17 +10443,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10592,32 +10596,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10625,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10649,17 +10657,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10669,12 +10677,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10707,32 +10715,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -10740,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10764,17 +10776,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10784,12 +10796,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10822,32 +10834,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10855,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10879,17 +10895,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10899,17 +10915,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10937,32 +10953,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10970,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10994,17 +11014,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11014,12 +11034,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11085,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11167,32 +11187,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11200,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11224,37 +11248,37 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11339,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11430,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11469,7 +11493,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11484,7 +11508,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11660,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11704,17 +11728,247 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
         </is>
       </c>
-      <c r="AC95" s="2" t="inlineStr">
-        <is>
-          <t>11/14</t>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-182路.xlsx
+++ b/data/export/2026-10-21-182路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8424,17 +8424,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8896,17 +8896,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9848,17 +9848,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10558,17 +10558,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10915,12 +10915,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10975,12 +10975,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11072,32 +11072,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11105,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11129,17 +11133,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11149,12 +11153,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11224,7 +11228,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11306,32 +11310,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11339,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11363,17 +11371,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11383,12 +11391,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11421,32 +11429,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11454,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11478,17 +11490,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11498,17 +11510,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11548,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11569,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11593,17 +11609,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11613,17 +11629,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11651,32 +11667,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -11684,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11708,17 +11728,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11728,12 +11748,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11799,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11914,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11958,17 +11978,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
